--- a/results/reliability_eval/Llama-3-8B_P1412_sample_15_tokens_0.1_temp_deductive_reasoning_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P1412_sample_15_tokens_0.1_temp_deductive_reasoning_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4298925488814515</v>
+        <v>0.3971479912719805</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1700304453872862</v>
+        <v>0.2230807827907046</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4298925488814515</v>
+        <v>0.3971479912719805</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1700304453872862</v>
+        <v>0.2230807827907046</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5600408405587197</v>
+        <v>0.6049929405724555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2869369487470185</v>
+        <v>0.3597064082484953</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9912936540556762</v>
+        <v>0.9983955846489538</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9587207946926617</v>
+        <v>0.9939931773556169</v>
       </c>
       <c r="I2" t="n">
-        <v>0.189</v>
+        <v>0.265</v>
       </c>
     </row>
   </sheetData>
